--- a/AAII_Financials/Quarterly/ZLAB_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZLAB_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="92">
   <si>
     <t>ZLAB</t>
   </si>
@@ -656,153 +656,154 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="39" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="40" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43465</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43373</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43281</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42551</v>
       </c>
-      <c r="AJ7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AK7" s="2" t="s">
         <v>3</v>
       </c>
@@ -812,97 +813,100 @@
       <c r="AM7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AN7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>106300</v>
+      </c>
+      <c r="E8" s="3">
         <v>99600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>127600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>116100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>110000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>106500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>109100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>102300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>100500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>87100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>65800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>69200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>68900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>62800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>62600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>57500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>48200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>46700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>44200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>43100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>36900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>20100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>29700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>19200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>100</v>
       </c>
-      <c r="AE8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="3" t="s">
-        <v>3</v>
+      <c r="AF8" s="3">
+        <v>0</v>
       </c>
       <c r="AG8" s="3" t="s">
         <v>3</v>
@@ -916,8 +920,8 @@
       <c r="AJ8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AK8" s="3">
-        <v>0</v>
+      <c r="AK8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AL8" s="3">
         <v>0</v>
@@ -925,94 +929,97 @@
       <c r="AM8" s="3">
         <v>0</v>
       </c>
+      <c r="AN8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>109900</v>
+      </c>
+      <c r="E9" s="3">
         <v>103900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>124000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>94800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>93800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>99400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>94300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>102900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>96900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>88300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>107200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>84200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>-9400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>69800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>20900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>20000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>17400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>15600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>21700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>10900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>11800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>900</v>
       </c>
-      <c r="AD9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="3" t="s">
-        <v>3</v>
+      <c r="AE9" s="3">
+        <v>0</v>
       </c>
       <c r="AF9" s="3" t="s">
         <v>3</v>
@@ -1038,95 +1045,98 @@
       <c r="AM9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E10" s="3">
         <v>-4300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>21300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>16100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>14700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-1100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-41400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-15000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>78200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>41700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>37500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>30800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>31100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>22500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>30900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>26000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>12600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>17900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>14200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>6700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>100</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1151,8 +1161,11 @@
       <c r="AM10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1192,110 +1205,111 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>61800</v>
+      </c>
+      <c r="E12" s="3">
         <v>65600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>61600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>47900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>50600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>60700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>52300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>66000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>61600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>54600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>81900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>58800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>109800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>48500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>66900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>99500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>66100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>53900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>172100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>55100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>142200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>203900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>120700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>102000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>83300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>51200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>58900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>85600</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>30000</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>34600</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>18500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>20900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>8800</v>
       </c>
-      <c r="AJ12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1305,8 +1319,11 @@
       <c r="AM12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1418,55 +1435,58 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>1900</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>10000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-4900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-4800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-8300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-400</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1531,13 +1551,16 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>3900</v>
+        <v>4200</v>
       </c>
       <c r="E15" s="3">
         <v>3900</v>
@@ -1546,38 +1569,38 @@
         <v>3900</v>
       </c>
       <c r="G15" s="3">
+        <v>3900</v>
+      </c>
+      <c r="H15" s="3">
         <v>3700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>2900</v>
       </c>
       <c r="K15" s="3">
         <v>2900</v>
       </c>
       <c r="L15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="M15" s="3">
         <v>3000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2700</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1644,8 +1667,11 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1682,110 +1708,111 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>182800</v>
+      </c>
+      <c r="E17" s="3">
         <v>169000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>197000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>164900</v>
       </c>
       <c r="G17" s="3">
         <v>164900</v>
       </c>
       <c r="H17" s="3">
+        <v>164900</v>
+      </c>
+      <c r="I17" s="3">
         <v>162800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>177000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>170100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>176600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>157500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>189800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>152800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>168400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>132300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>159900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>186100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>146900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>126500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>263400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>126300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>207500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>247200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>201300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>149500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>126900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>70200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>89300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>100900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>34200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>41000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>26500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>24900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>11200</v>
       </c>
-      <c r="AJ17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1795,98 +1822,101 @@
       <c r="AM17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-69400</v>
+        <v>-76500</v>
       </c>
       <c r="E18" s="3">
         <v>-69400</v>
       </c>
       <c r="F18" s="3">
+        <v>-69400</v>
+      </c>
+      <c r="G18" s="3">
         <v>-48800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-54900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-56300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-67900</v>
       </c>
       <c r="J18" s="3">
         <v>-67900</v>
       </c>
       <c r="K18" s="3">
+        <v>-67900</v>
+      </c>
+      <c r="L18" s="3">
         <v>-76100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-70300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-124000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-83600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-99500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-69500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-97300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-128600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-98700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-79800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-219200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-83200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-170600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-227100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-171600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-130300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-117300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-65300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-85900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-100800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-34200</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1908,8 +1938,11 @@
       <c r="AM18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1949,98 +1982,99 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-15000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-10200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-5900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-6600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>21900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-18800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-13500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>39700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>35500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-32600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-39200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>7900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-12900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>7700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>32100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>5900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
@@ -2062,89 +2096,92 @@
       <c r="AM20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-50400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-55300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-39000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-44600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-50500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-86800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-46200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-76100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-64900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-108000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-75700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-137200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-57200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-59600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-159000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-136100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-80200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-209400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-94400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-161400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-231700</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-62700</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2175,8 +2212,11 @@
       <c r="AM21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2184,32 +2224,32 @@
         <v>1600</v>
       </c>
       <c r="E22" s="3">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="F22" s="3">
         <v>1400</v>
       </c>
       <c r="G22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H22" s="3">
         <v>1300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
@@ -2231,8 +2271,8 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -2244,25 +2284,25 @@
         <v>0</v>
       </c>
       <c r="Y22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="3">
         <v>100</v>
       </c>
       <c r="AA22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD22" s="3">
         <v>300</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="3" t="s">
-        <v>3</v>
+      <c r="AE22" s="3">
+        <v>0</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>3</v>
@@ -2279,8 +2319,8 @@
       <c r="AJ22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AK22" s="3">
-        <v>0</v>
+      <c r="AK22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AL22" s="3">
         <v>0</v>
@@ -2288,110 +2328,113 @@
       <c r="AM22" s="3">
         <v>0</v>
       </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-51800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-49600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-53300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-36000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-40700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-48400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-81700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-41700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-80300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-53500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-95400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-69200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-120900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-49100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-61800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-161200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-137900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-82200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-211300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-96100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-162900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-233100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-139600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-128200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-111300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-65200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-83000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-97200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-34100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-41300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-25700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-24400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-11800</v>
       </c>
-      <c r="AJ23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2401,20 +2444,23 @@
       <c r="AM23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2900</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2445,8 +2491,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2514,8 +2560,11 @@
       <c r="AM24" s="3">
         <v>0</v>
       </c>
+      <c r="AN24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2627,110 +2676,113 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-51000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-50400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-36000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-40700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-48400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-81700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-41700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-80300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-53500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-95400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-69200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-120900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-49100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-61800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-161200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-137900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-82200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-211300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-96100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-162900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-233100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-139600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-128200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-111300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-65200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-83000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-97200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-34100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-41300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-25700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-24400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AJ26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2740,110 +2792,113 @@
       <c r="AM26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-51000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-50400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-36000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-40700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-48400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-81700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-41700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-80300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-53500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-95400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-69200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-120900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-49100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-61800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-161200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-137900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-82400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-211800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-96400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-163300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-232900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-140300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-128600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-111800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-65400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-83300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-97600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-34200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-41500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-26000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-24400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AJ27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2853,8 +2908,11 @@
       <c r="AM27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2966,8 +3024,11 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3079,8 +3140,11 @@
       <c r="AM29" s="3">
         <v>0</v>
       </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3192,8 +3256,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3305,98 +3372,101 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E32" s="3">
         <v>15000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>10200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>5900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>6600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-21900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>18800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>13500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-39700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-35500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>32600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>39200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-7900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>12900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-7700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>6000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-32100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-5900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
@@ -3418,110 +3488,113 @@
       <c r="AM32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-51000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-50400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-36000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-40700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-48400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-81700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-41700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-80300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-53500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-95400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-69200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-120900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-49100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-61800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-161200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-137900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-82400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-211800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-96400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-163300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-232900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-140300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-128600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-111800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-65400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-83300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-97600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-34200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-41500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-26000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-24400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-11800</v>
       </c>
-      <c r="AJ33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3531,8 +3604,11 @@
       <c r="AM33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3644,110 +3720,113 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-51000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-50400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-36000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-40700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-48400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-81700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-41700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-80300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-53500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-95400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-69200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-120900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-49100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-61800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-161200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-137900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-82400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-211800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-96400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-163300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-232900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-140300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-128600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-111800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-65400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-83300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-97600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-34200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-41500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-26000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-24400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-11800</v>
       </c>
-      <c r="AJ35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3757,115 +3836,118 @@
       <c r="AM35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43465</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43373</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43281</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42551</v>
       </c>
-      <c r="AJ38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AK38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3875,8 +3957,11 @@
       <c r="AM38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AN38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3916,8 +4001,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3957,104 +4043,105 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>607500</v>
+      </c>
+      <c r="E41" s="3">
         <v>651300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>679600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>717200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>732200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>757300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>449700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>616100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>630000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>650800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>790200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>788800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>859200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>879800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1008500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1119500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>680800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>847000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>964100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1398500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1766600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1013400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>442100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>258600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>75900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>68700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>91600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>63000</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF41" s="3">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG41" s="3">
         <v>127700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>229700</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
@@ -4070,8 +4157,11 @@
       <c r="AM41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4082,7 +4172,7 @@
         <v>10000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
@@ -4091,11 +4181,11 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>330000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -4103,68 +4193,68 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>16300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>31600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>15500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>50600</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
       <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
         <v>575300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>465300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>445000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>170000</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
       <c r="X42" s="3">
         <v>0</v>
       </c>
       <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
         <v>744700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>205000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>200000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>251600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>301600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>200400</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF42" s="3">
+      <c r="AF42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG42" s="3">
         <v>50000</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH42" s="3" t="s">
         <v>3</v>
       </c>
@@ -4174,8 +4264,8 @@
       <c r="AJ42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AK42" s="3">
-        <v>0</v>
+      <c r="AK42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AL42" s="3">
         <v>0</v>
@@ -4183,95 +4273,98 @@
       <c r="AM42" s="3">
         <v>0</v>
       </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E43" s="3">
         <v>62000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>118300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>105000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>99300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>87700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>89400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>69200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>77700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>75800</v>
-      </c>
-      <c r="M43" s="3">
-        <v>65300</v>
       </c>
       <c r="N43" s="3">
         <v>65300</v>
       </c>
       <c r="O43" s="3">
+        <v>65300</v>
+      </c>
+      <c r="P43" s="3">
         <v>68100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>60700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>48600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>39100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>38200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>44200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>54800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>21000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>18000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>100</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4287,8 +4380,8 @@
       <c r="AJ43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AK43" s="3">
-        <v>0</v>
+      <c r="AK43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AL43" s="3">
         <v>0</v>
@@ -4296,94 +4389,97 @@
       <c r="AM43" s="3">
         <v>0</v>
       </c>
+      <c r="AN43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>90900</v>
+      </c>
+      <c r="E44" s="3">
         <v>86000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>74700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>67100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>61700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>53100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>39900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>39500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>41800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>37900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>44800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>44200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>36400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>38400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>31600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>29100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>23300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>20300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>19000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>12500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>11100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>12600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>13100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>6600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>100</v>
       </c>
-      <c r="AD44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE44" s="3" t="s">
-        <v>3</v>
+      <c r="AE44" s="3">
+        <v>0</v>
       </c>
       <c r="AF44" s="3" t="s">
         <v>3</v>
@@ -4400,8 +4496,8 @@
       <c r="AJ44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AK44" s="3">
-        <v>0</v>
+      <c r="AK44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AL44" s="3">
         <v>0</v>
@@ -4409,104 +4505,107 @@
       <c r="AM44" s="3">
         <v>0</v>
       </c>
+      <c r="AN44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E45" s="3">
         <v>35500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>36700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>43700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>40800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>43900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>41500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>35700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>20300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>24200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>23000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>29800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>38400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>42800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>35700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>22200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>18000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>16500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>18000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>17100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>12900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>14300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>10900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>6000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5700</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF45" s="3">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG45" s="3">
         <v>4700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1000</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4522,104 +4621,107 @@
       <c r="AM45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>914000</v>
+      </c>
+      <c r="E46" s="3">
         <v>944700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1019300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1032900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1034100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1041900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1050500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>860500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>869900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>888600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>939600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>959700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1017500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1072300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1124300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1209800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1335600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1393300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1500900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1619100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1808600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1049200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1216000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>484900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>292500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>329300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>401800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>269100</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF46" s="3">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG46" s="3">
         <v>182400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>230600</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4635,8 +4737,11 @@
       <c r="AM46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4658,81 +4763,81 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>3200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>14100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>5100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>29200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>39500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>44200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>24900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>25200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>23400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>18200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>16100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>17100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>14000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>11200</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF47" s="3">
+      <c r="AF47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG47" s="3">
         <v>3500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>6700</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4748,104 +4853,107 @@
       <c r="AM47" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN47" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E48" s="3">
         <v>64700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>66500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>64600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>66900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>68700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>69500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>63600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>63700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>67600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>68600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>71700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>74900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>78500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>77400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>70800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>65000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>62200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>57300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>52600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>48700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>45700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>46900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>34900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>36400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>35300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>29600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>20500</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG48" s="3">
         <v>19500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>11900</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4861,49 +4969,52 @@
       <c r="AM48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>88700</v>
+      </c>
+      <c r="E49" s="3">
         <v>78600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>79000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>58100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>59400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>59100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>58900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>54700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>47100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4800</v>
-      </c>
-      <c r="P49" s="3">
-        <v>8400</v>
       </c>
       <c r="Q49" s="3">
         <v>8400</v>
@@ -4912,52 +5023,52 @@
         <v>8400</v>
       </c>
       <c r="S49" s="3">
+        <v>8400</v>
+      </c>
+      <c r="T49" s="3">
         <v>9000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>9400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>9600</v>
-      </c>
-      <c r="X49" s="3">
-        <v>9400</v>
       </c>
       <c r="Y49" s="3">
         <v>9400</v>
       </c>
       <c r="Z49" s="3">
+        <v>9400</v>
+      </c>
+      <c r="AA49" s="3">
         <v>8600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>300</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="3" t="s">
-        <v>3</v>
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
       </c>
       <c r="AI49" s="3" t="s">
         <v>3</v>
@@ -4974,8 +5085,11 @@
       <c r="AM49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5087,8 +5201,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5200,104 +5317,107 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E52" s="3">
         <v>4300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3200</v>
-      </c>
-      <c r="O52" s="3">
-        <v>4000</v>
       </c>
       <c r="P52" s="3">
         <v>4000</v>
       </c>
       <c r="Q52" s="3">
+        <v>4000</v>
+      </c>
+      <c r="R52" s="3">
         <v>3600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3500</v>
-      </c>
-      <c r="X52" s="3">
-        <v>1900</v>
       </c>
       <c r="Y52" s="3">
         <v>1900</v>
       </c>
       <c r="Z52" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AA52" s="3">
         <v>1600</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>1300</v>
       </c>
       <c r="AB52" s="3">
         <v>1300</v>
       </c>
       <c r="AC52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AD52" s="3">
         <v>400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>800</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF52" s="3">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG52" s="3">
         <v>5400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>400</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI52" s="3" t="s">
         <v>3</v>
       </c>
@@ -5313,8 +5433,11 @@
       <c r="AM52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5426,104 +5549,107 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1074800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1095700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1172400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1158900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1164100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1173300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1185800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>985300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>987400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>988400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1036300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1043700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1106400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1170100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1220100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1298500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1418800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1500900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1610000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1728100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1895200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1131300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1297600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>548200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>355200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>391600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>446500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>302000</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF54" s="3">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG54" s="3">
         <v>210800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>249600</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5539,8 +5665,11 @@
       <c r="AM54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5580,8 +5709,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5621,104 +5751,105 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>136700</v>
+      </c>
+      <c r="E57" s="3">
         <v>126200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>141600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>99700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>107400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>103000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>100900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>120700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>127300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>88100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>113000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>55000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>67000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>66400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>66000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>90100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>108400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>98200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>126200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>51400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>125600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>41400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>62600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>32400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>22700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>20500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>27700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>37400</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG57" s="3">
         <v>5700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9000</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5734,58 +5865,61 @@
       <c r="AM57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>243100</v>
+      </c>
+      <c r="E58" s="3">
         <v>219800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>210900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>208500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>180100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>180000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>139800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>119600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>77900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>55800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6900</v>
-      </c>
-      <c r="O58" s="3">
-        <v>7300</v>
       </c>
       <c r="P58" s="3">
         <v>7300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
+      <c r="Q58" s="3">
+        <v>7300</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -5799,36 +5933,36 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>4200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>6500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>6400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>5800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3600</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF58" s="3">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG58" s="3">
         <v>800</v>
       </c>
-      <c r="AG58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5838,8 +5972,8 @@
       <c r="AJ58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AK58" s="3">
-        <v>0</v>
+      <c r="AK58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AL58" s="3">
         <v>0</v>
@@ -5847,104 +5981,107 @@
       <c r="AM58" s="3">
         <v>0</v>
       </c>
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E59" s="3">
         <v>10800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>24800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>23600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>73900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>65400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>60400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>56800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>66700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>60600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>68300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>51200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>35400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>19900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>17500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>14200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>12400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7800</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG59" s="3">
         <v>3800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3100</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5960,104 +6097,107 @@
       <c r="AM59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>428600</v>
+      </c>
+      <c r="E60" s="3">
         <v>393000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>416200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>359800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>331500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>319800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>299400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>286300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>251700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>192100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>203100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>124900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>133400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>124600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>139800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>155500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>168900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>154900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>192900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>112000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>193900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>92700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>98000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>56600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>46600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>41100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>46000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>48800</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF60" s="3">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG60" s="3">
         <v>10300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>12100</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
@@ -6073,53 +6213,56 @@
       <c r="AM60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E61" s="3">
         <v>12100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>13400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>9800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -6186,19 +6329,22 @@
       <c r="AM61" s="3">
         <v>0</v>
       </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3">
-        <v>300</v>
+        <v>200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G62" s="3">
         <v>300</v>
@@ -6231,59 +6377,59 @@
         <v>300</v>
       </c>
       <c r="Q62" s="3">
+        <v>300</v>
+      </c>
+      <c r="R62" s="3">
         <v>34700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>37100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>37700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>38000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>37100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>28100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>29600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>29000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>30300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>26200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>13900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>13500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2100</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG62" s="3">
         <v>1600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2400</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI62" s="3" t="s">
         <v>3</v>
       </c>
@@ -6299,8 +6445,11 @@
       <c r="AM62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6412,8 +6561,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6525,8 +6677,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6638,104 +6793,107 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>467800</v>
+      </c>
+      <c r="E66" s="3">
         <v>433800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>456900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>399000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>372400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>362600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>344900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>317700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>283200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>226300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>240200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>162700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>174100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>168800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>174500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>192600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>206600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>192900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>230000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>140100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>223500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>121600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>128300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>82700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>60500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>54500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>53100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>50900</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF66" s="3">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG66" s="3">
         <v>11900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>14500</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6751,8 +6909,11 @@
       <c r="AM66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6792,8 +6953,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6905,8 +7067,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7018,8 +7183,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7131,8 +7299,11 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7244,104 +7415,107 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2730500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2679600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2628600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2578200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2542200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2501500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2453100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2371400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-2329700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-2249500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-2196000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-2100600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-2031400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1910500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1861400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1799600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1638400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1500500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1418100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1206200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-1109800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-946500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-713600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-573300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-444700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-398300</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE72" s="3">
         <v>-249600</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH72" s="3">
         <v>-110600</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7357,8 +7531,11 @@
       <c r="AM72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7470,8 +7647,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7583,8 +7763,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7696,104 +7879,107 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>607000</v>
+      </c>
+      <c r="E76" s="3">
         <v>662000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>715500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>759900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>791700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>810800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>840900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>667700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>704200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>762200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>796100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>881000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>932300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1001200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1045600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1105900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1212200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1308000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1380000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1587900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1671700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1009700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1169300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>465500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>294700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>337100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>393300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>251100</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF76" s="3">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG76" s="3">
         <v>198900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>235200</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7809,8 +7995,11 @@
       <c r="AM76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7922,115 +8111,118 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43465</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43373</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43281</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42551</v>
       </c>
-      <c r="AJ80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AK80" s="2" t="s">
         <v>3</v>
       </c>
@@ -8040,110 +8232,113 @@
       <c r="AM80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AN80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-51000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-50400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-36000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-40700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-48400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-81700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-41700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-80300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-53500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-95400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-69200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-120900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-49100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-61800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-161200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-137900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-82400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-211800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-96400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-163300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-232900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-140300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-128600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-111800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-65400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-83300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-97600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-34200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-41500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-26000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-24400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-11800</v>
       </c>
-      <c r="AJ81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK81" s="3" t="s">
         <v>3</v>
       </c>
@@ -8153,8 +8348,11 @@
       <c r="AM81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8194,16 +8392,17 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E83" s="3">
         <v>2000</v>
-      </c>
-      <c r="E83" s="3">
-        <v>2100</v>
       </c>
       <c r="F83" s="3">
         <v>2100</v>
@@ -8212,76 +8411,76 @@
         <v>2100</v>
       </c>
       <c r="H83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I83" s="3">
         <v>2300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1400</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC83" s="3">
         <v>2500</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE83" s="3">
-        <v>0</v>
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF83" s="3">
         <v>0</v>
@@ -8292,8 +8491,8 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>3</v>
+      <c r="AI83" s="3">
+        <v>0</v>
       </c>
       <c r="AJ83" s="3" t="s">
         <v>3</v>
@@ -8307,8 +8506,11 @@
       <c r="AM83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8420,8 +8622,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8533,8 +8738,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8646,8 +8854,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8759,8 +8970,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8872,94 +9086,97 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-63400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-11900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-26000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-32000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-31000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-61700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-55800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-26800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-42200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-90100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-14900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-55300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-58700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-69300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-109300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-126300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-44900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-87100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-153000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-160900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-65800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-169500</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-151000</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF89" s="3">
         <v>0</v>
@@ -8970,8 +9187,8 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-      <c r="AI89" s="3" t="s">
-        <v>3</v>
+      <c r="AI89" s="3">
+        <v>0</v>
       </c>
       <c r="AJ89" s="3" t="s">
         <v>3</v>
@@ -8985,8 +9202,11 @@
       <c r="AM89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9026,94 +9246,95 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF91" s="3">
         <v>0</v>
@@ -9124,8 +9345,8 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-      <c r="AI91" s="3" t="s">
-        <v>3</v>
+      <c r="AI91" s="3">
+        <v>0</v>
       </c>
       <c r="AJ91" s="3" t="s">
         <v>3</v>
@@ -9139,8 +9360,11 @@
       <c r="AM91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9252,8 +9476,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9365,94 +9592,97 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-22300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>326100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-347800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-29900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>3300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>14500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-14000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>42700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>568300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-113700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-30100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-281500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-206400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>742000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-64500</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF94" s="3">
         <v>0</v>
@@ -9463,8 +9693,8 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-      <c r="AI94" s="3" t="s">
-        <v>3</v>
+      <c r="AI94" s="3">
+        <v>0</v>
       </c>
       <c r="AJ94" s="3" t="s">
         <v>3</v>
@@ -9478,8 +9708,11 @@
       <c r="AM94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9519,8 +9752,9 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9563,8 +9797,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -9632,8 +9866,11 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9745,8 +9982,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9858,8 +10098,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9971,94 +10214,97 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E100" s="3">
         <v>5600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>20800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>8800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>43100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>237800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>42200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>22300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>47500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>821200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-300</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC100" s="3">
         <v>218500</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF100" s="3">
         <v>0</v>
@@ -10069,8 +10315,8 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-      <c r="AI100" s="3" t="s">
-        <v>3</v>
+      <c r="AI100" s="3">
+        <v>0</v>
       </c>
       <c r="AJ100" s="3" t="s">
         <v>3</v>
@@ -10084,94 +10330,97 @@
       <c r="AM100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-5000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-900</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC101" s="3">
         <v>3300</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
+      <c r="AE101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF101" s="3">
         <v>0</v>
@@ -10182,8 +10431,8 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-      <c r="AI101" s="3" t="s">
-        <v>3</v>
+      <c r="AI101" s="3">
+        <v>0</v>
       </c>
       <c r="AJ101" s="3" t="s">
         <v>3</v>
@@ -10197,94 +10446,97 @@
       <c r="AM101" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN101" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-28300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-37600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-25000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>307600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-166400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-20700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-39400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-70300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-19900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-128400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-111000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>438700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-166100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-117100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-434300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-368100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>753200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>571300</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3">
         <v>6300</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
+      <c r="AE102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF102" s="3">
         <v>0</v>
@@ -10295,8 +10547,8 @@
       <c r="AH102" s="3">
         <v>0</v>
       </c>
-      <c r="AI102" s="3" t="s">
-        <v>3</v>
+      <c r="AI102" s="3">
+        <v>0</v>
       </c>
       <c r="AJ102" s="3" t="s">
         <v>3</v>
@@ -10308,6 +10560,9 @@
         <v>3</v>
       </c>
       <c r="AM102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
